--- a/stories/arbres/TREE-DIF-068.xlsx
+++ b/stories/arbres/TREE-DIF-068.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Kenzo est avec maman, à la maison. Kenzo a envie de jouer. maman est là, tout près. On va apprendre : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo écoute maman. Kenzo entend les mots : pas rire de l'apparence.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Kenzo respire. Kenzo retient : pas rire de l'apparence. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Kenzo respire. Kenzo retient : pas rire de l'apparence. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Kenzo va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Kenzo se souvient : pas rire de l'apparence. Voici le geste : jouer ; pas rire. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Kenzo respire. Kenzo retient : pas rire de l'apparence. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-068.xlsx
+++ b/stories/arbres/TREE-DIF-068.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Kenzo est avec maman, à la maison. Kenzo a envie de jouer. maman est là, tout près. On va apprendre : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo écoute maman. Kenzo entend les mots : pas rire de l'apparence.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Kenzo respire. Kenzo retient : pas rire de l'apparence. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Kenzo a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Kenzo rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Kenzo rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Kenzo rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Kenzo a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Kenzo rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Kenzo rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Kenzo rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Kenzo a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Kenzo rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Kenzo rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Kenzo rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Kenzo respire. Kenzo retient : pas rire de l'apparence. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Kenzo a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Kenzo rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Kenzo rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Kenzo rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Kenzo a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Kenzo rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Kenzo rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Kenzo rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Kenzo a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Kenzo rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Kenzo rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Kenzo rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Lunettes, cheveux, habit.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas rire. Kenzo respire. Kenzo retient : pas rire de l'apparence. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Kenzo a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Kenzo rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Kenzo rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Kenzo rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Kenzo a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Kenzo rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Kenzo rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Kenzo rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Kenzo a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer ; pas rire. Kenzo répète tout bas : pas rire de l'apparence. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Kenzo rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Kenzo rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Kenzo rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Kenzo a appris : Lunettes, cheveux, habit. Voici le geste : jouer ; pas rire. Kenzo a entendu : pas rire de l'apparence. Kenzo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-068.xlsx
+++ b/stories/arbres/TREE-DIF-068.xlsx
@@ -2543,17 +2543,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?</t>
+          <t>Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -2713,6 +2713,7 @@
         <is>
           <t>narrateur|Le soleil cache le clou, trop blanc.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 maman|Tu vois le grain, toi ?
 papa|Les lunettes, Mila tient, ou le nuage ?</t>
         </is>
@@ -2741,17 +2742,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tes lunettes, d'abord. Elle baisse les lunettes, trop vite, trop fort. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, un peu. La photo, moi. Mila tient le cadre, plus bas, plus lent. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment faire. Le portrait monte, droit, à son rythme.</t>
+          <t>Tes lunettes, d'abord. Elle baisse les lunettes, trop vite, trop fort. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, un peu. La photo, moi. Mila tient le cadre, plus bas, plus lent. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment faire. Ça a failli ne pas tenir. Le portrait monte, droit, à son rythme.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tes &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, trop vite, trop fort. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, un peu. La photo, moi. Mila tient le cadre, plus bas, plus lent. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment faire. Le portrait monte, droit, à son rythme.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tes &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, trop vite, trop fort. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, un peu. La photo, moi. Mila tient le cadre, plus bas, plus lent. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment faire. Ça a failli ne pas tenir. Le portrait monte, droit, à son rythme.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Tes &lt;emphasis&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, trop vite, trop fort. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, un peu. La photo, moi. Mila tient le cadre, plus bas, plus lent. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment faire. Le portrait monte, droit, à son rythme. [pause]</t>
+          <t>Tes &lt;emphasis&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, trop vite, trop fort. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, un peu. La photo, moi. Mila tient le cadre, plus bas, plus lent. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment faire. Ça a failli ne pas tenir. Le portrait monte, droit, à son rythme. [pause]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2895,6 +2896,7 @@
 enfant-f|Oui, le grain est dessus.
 maman|Vous l'avez, toutes les deux.
 narrateur|Personne n'a dit comment faire.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, droit, à son rythme.</t>
         </is>
       </c>
@@ -2927,17 +2929,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli rester trop blanc. Les lunettes ont laissé le clou. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le cadre reste droit, contre le mur. Mila a tenu, à sa façon. Un grain de cire claire reste au coin du cadre.</t>
+          <t>Le portrait a failli rester trop blanc. Les lunettes ont laissé le clou. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le cadre reste droit, contre le mur. Mila a tenu, à sa façon. Le petit toc du début s'est tu. Un grain de cire claire reste au coin du cadre.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli rester trop blanc. Les lunettes ont laissé le clou. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le cadre reste droit, contre le mur. Mila a tenu, à sa façon. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; reste au coin du cadre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli rester trop blanc. Les lunettes ont laissé le clou. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le cadre reste droit, contre le mur. Mila a tenu, à sa façon. Le petit toc du début s'est tu. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; reste au coin du cadre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli rester trop blanc. Les lunettes ont laissé le clou. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le cadre reste droit, contre le mur. Mila a tenu, à sa façon. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; reste au coin du cadre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli rester trop blanc. Les lunettes ont laissé le clou. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le cadre reste droit, contre le mur. Mila a tenu, à sa façon. Le petit toc du début s'est tu. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; reste au coin du cadre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -3081,6 +3083,7 @@
 papa|On descend, le palier sent la cire.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|Mila a tenu, à sa façon.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Un grain de cire claire reste au coin du cadre.</t>
         </is>
       </c>
@@ -3113,17 +3116,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens, Mila. Elle lâche un peu, sans arracher le cadre. Mila tient à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, tout bas. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Le portrait monte, porté par Mila.</t>
+          <t>Tu tiens, Mila. Elle lâche un peu, sans arracher le cadre. Mila tient à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, tout bas. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le portrait monte, porté par Mila.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu tiens, &lt;emphasis level="moderate"&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans arracher le cadre. Mila tient à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, tout bas. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Le portrait monte, porté par Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu tiens, &lt;emphasis level="moderate"&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans arracher le cadre. Mila tient à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, tout bas. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le portrait monte, porté par Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens, &lt;emphasis&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans arracher le cadre. Mila tient à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, tout bas. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Le portrait monte, porté par Mila. [pause]</t>
+          <t>Tu tiens, &lt;emphasis&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans arracher le cadre. Mila tient à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, tout bas. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le portrait monte, porté par Mila. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3267,6 +3270,7 @@
 enfant-f|On monte, après.
 maman|Le clou attend, un peu.
 narrateur|Personne n'a crié la réponse.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, porté par Mila.</t>
         </is>
       </c>
@@ -3299,17 +3303,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli rester trop bas. Je l'ai tenu, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le cadre reste droit, contre le mur. Ses mains ont choisi la hauteur. Le grain de cire claire brille, là où Mila a tenu.</t>
+          <t>Le portrait a failli rester trop bas. Je l'ai tenu, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le cadre reste droit, contre le mur. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le grain de cire claire brille, là où Mila a tenu.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli rester trop bas. Je l'ai tenu, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le cadre reste droit, contre le mur. Ses mains ont choisi la hauteur. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille, là où Mila a tenu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli rester trop bas. Je l'ai tenu, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le cadre reste droit, contre le mur. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille, là où Mila a tenu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli rester trop bas. Je l'ai tenu, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le cadre reste droit, contre le mur. Ses mains ont choisi la hauteur. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille, là où Mila a tenu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli rester trop bas. Je l'ai tenu, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le cadre reste droit, contre le mur. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille, là où Mila a tenu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3453,6 +3457,7 @@
 papa|On descend, les mains un peu grasses.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|Ses mains ont choisi la hauteur.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire brille, là où Mila a tenu.</t>
         </is>
       </c>
@@ -3485,17 +3490,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le nuage, d'abord. Elle attend, le cadre contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila lève le cadre, à son heure. Le soleil a laissé le clou. On accroche, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le portrait monte, sans le blanc.</t>
+          <t>Le nuage, d'abord. Elle attend, le cadre contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila lève le cadre, à son heure. Le soleil a laissé le clou. On accroche, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le portrait monte, sans le blanc.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le cadre contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila lève le cadre, à son heure. Le soleil a laissé le clou. On accroche, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le portrait monte, sans le blanc.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le cadre contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila lève le cadre, à son heure. Le soleil a laissé le clou. On accroche, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le portrait monte, sans le blanc.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le cadre contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila lève le cadre, à son heure. Le soleil a laissé le clou. On accroche, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le portrait monte, sans le blanc. [pause]</t>
+          <t>Le &lt;emphasis&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le cadre contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila lève le cadre, à son heure. Le soleil a laissé le clou. On accroche, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le portrait monte, sans le blanc. [pause]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3639,6 +3644,7 @@
 enfant-f|On accroche, lentement.
 maman|Vous avez attendu ensemble.
 narrateur|Personne n'a pressé le nuage.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, sans le blanc.</t>
         </is>
       </c>
@@ -3671,17 +3677,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli attendre le soleil. Le nuage a passé. Puis on a accroché, sans le blanc. On descend, la fenêtre ronde est grise. Le cadre reste droit, contre le mur. On a attendu le nuage, toutes les deux. Le grain de cire claire reparaît, après le nuage.</t>
+          <t>Le portrait a failli attendre le soleil. Le nuage a passé. Puis on a accroché, sans le blanc. On descend, la fenêtre ronde est grise. Le cadre reste droit, contre le mur. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le grain de cire claire reparaît, après le nuage.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli attendre le soleil. Le nuage a passé. Puis on a accroché, sans le blanc. On descend, la fenêtre ronde est grise. Le cadre reste droit, contre le mur. On a attendu le nuage, toutes les deux. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; reparaît, après le nuage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli attendre le soleil. Le nuage a passé. Puis on a accroché, sans le blanc. On descend, la fenêtre ronde est grise. Le cadre reste droit, contre le mur. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; reparaît, après le nuage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli attendre le soleil. Le nuage a passé. Puis on a accroché, sans le blanc. On descend, la fenêtre ronde est grise. Le cadre reste droit, contre le mur. On a attendu le nuage, toutes les deux. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; reparaît, après le nuage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli attendre le soleil. Le nuage a passé. Puis on a accroché, sans le blanc. On descend, la fenêtre ronde est grise. Le cadre reste droit, contre le mur. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; reparaît, après le nuage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -3825,6 +3831,7 @@
 papa|On descend, la fenêtre ronde est grise.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|On a attendu le nuage, toutes les deux.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire reparaît, après le nuage.</t>
         </is>
       </c>
@@ -4050,17 +4057,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?</t>
+          <t>Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -4220,6 +4227,7 @@
         <is>
           <t>narrateur|Les cheveux gênent, contre la rampe.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 papa|Tu vois le grain, toi ?
 maman|Le nœud, l'oreille, ou Mila souffle ?</t>
         </is>
@@ -4248,17 +4256,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Un nœud, dans tes cheveux. Elle tend un élastique, trop vite. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au coin. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le portrait monte, le nœud tenu.</t>
+          <t>Un nœud, dans tes cheveux. Elle tend un élastique, trop vite. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au coin. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le portrait monte, le nœud tenu.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un &lt;emphasis level="moderate"&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, trop vite. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au coin. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le portrait monte, le nœud tenu.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un &lt;emphasis level="moderate"&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, trop vite. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au coin. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le portrait monte, le nœud tenu.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Un &lt;emphasis&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, trop vite. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au coin. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le portrait monte, le nœud tenu. [pause]</t>
+          <t>Un &lt;emphasis&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, trop vite. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au coin. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le portrait monte, le nœud tenu. [pause]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4402,6 +4410,7 @@
 enfant-f|La bouche est libre.
 maman|La rampe peut attendre.
 narrateur|Personne n'a tiré les cheveux.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, le nœud tenu.</t>
         </is>
       </c>
@@ -4434,17 +4443,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a accroché, la bouche libre. On descend, la rampe est lisse. Le cadre reste droit, contre le mur. Ses doigts ont noué, lentement. Un grain de cire claire colle au nœud, minuscule.</t>
+          <t>Le portrait a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a accroché, la bouche libre. On descend, la rampe est lisse. Le cadre reste droit, contre le mur. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un grain de cire claire colle au nœud, minuscule.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a accroché, la bouche libre. On descend, la rampe est lisse. Le cadre reste droit, contre le mur. Ses doigts ont noué, lentement. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a accroché, la bouche libre. On descend, la rampe est lisse. Le cadre reste droit, contre le mur. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a accroché, la bouche libre. On descend, la rampe est lisse. Le cadre reste droit, contre le mur. Ses doigts ont noué, lentement. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a accroché, la bouche libre. On descend, la rampe est lisse. Le cadre reste droit, contre le mur. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4588,6 +4597,7 @@
 papa|On descend, la rampe est lisse.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|Ses doigts ont noué, lentement.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Un grain de cire claire colle au nœud, minuscule.</t>
         </is>
       </c>
@@ -4620,17 +4630,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>J'écoute, près de ton oreille. Elle se tait, le cadre contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, collé. Victorina baisse le cadre, vers l'oreille. Tu as entendu, sans parler dessus. On accroche, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le portrait monte, à voix basse.</t>
+          <t>J'écoute, près de ton oreille. Elle se tait, le cadre contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, collé. Victorina baisse le cadre, vers l'oreille. Tu as entendu, sans parler dessus. On accroche, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le portrait monte, à voix basse.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;J'écoute, près de ton &lt;emphasis level="moderate"&gt;oreille&lt;/emphasis&gt;. Elle se tait, le cadre contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, collé. Victorina baisse le cadre, vers l'oreille. Tu as entendu, sans parler dessus. On accroche, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le portrait monte, à voix basse.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;J'écoute, près de ton &lt;emphasis level="moderate"&gt;oreille&lt;/emphasis&gt;. Elle se tait, le cadre contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, collé. Victorina baisse le cadre, vers l'oreille. Tu as entendu, sans parler dessus. On accroche, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le portrait monte, à voix basse.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>J'écoute, près de ton &lt;emphasis&gt;oreille&lt;/emphasis&gt;. Elle se tait, le cadre contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, collé. Victorina baisse le cadre, vers l'oreille. Tu as entendu, sans parler dessus. On accroche, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le portrait monte, à voix basse. [pause]</t>
+          <t>J'écoute, près de ton &lt;emphasis&gt;oreille&lt;/emphasis&gt;. Elle se tait, le cadre contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, collé. Victorina baisse le cadre, vers l'oreille. Tu as entendu, sans parler dessus. On accroche, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le portrait monte, à voix basse. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4774,6 +4784,7 @@
 enfant-f|On accroche, plus bas.
 maman|Sa voix a choisi la hauteur.
 narrateur|Personne n'a donné le plan.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, à voix basse.</t>
         </is>
       </c>
@@ -4806,17 +4817,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le cadre reste droit, contre le mur. Sa voix a choisi, toute basse. Le grain de cire claire attend près de l'oreille de Mila.</t>
+          <t>Le portrait a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le cadre reste droit, contre le mur. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le grain de cire claire attend près de l'oreille de Mila.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le cadre reste droit, contre le mur. Sa voix a choisi, toute basse. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; attend près de l'oreille de Mila.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le cadre reste droit, contre le mur. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; attend près de l'oreille de Mila.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le cadre reste droit, contre le mur. Sa voix a choisi, toute basse. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; attend près de l'oreille de Mila.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le cadre reste droit, contre le mur. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; attend près de l'oreille de Mila.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4960,6 +4971,7 @@
 papa|On descend, sans crier.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|Sa voix a choisi, toute basse.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire attend près de l'oreille de Mila.</t>
         </is>
       </c>
@@ -4992,17 +5004,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tu souffles, Mila. Elle attend, les lèvres fermées. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina lève le cadre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le portrait monte, après son air.</t>
+          <t>Tu souffles, Mila. Elle attend, les lèvres fermées. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina lève le cadre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le portrait monte, après son air.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu &lt;emphasis level="moderate"&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, les lèvres fermées. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina lève le cadre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le portrait monte, après son air.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu &lt;emphasis level="moderate"&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, les lèvres fermées. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina lève le cadre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le portrait monte, après son air.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tu &lt;emphasis&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, les lèvres fermées. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina lève le cadre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le portrait monte, après son air. [pause]</t>
+          <t>Tu &lt;emphasis&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, les lèvres fermées. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina lève le cadre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le portrait monte, après son air. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5146,6 +5158,7 @@
 enfant-f|La bouche est libre.
 maman|La rampe n'a plus pris les cheveux.
 narrateur|Personne n'a soufflé à sa place.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, après son air.</t>
         </is>
       </c>
@@ -5178,17 +5191,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli garder le cheveu. J'ai soufflé, moi. Puis on a accroché, après l'air. On descend, la rampe est libre. Le cadre reste droit, contre le mur. Son souffle a passé, d'abord. Le grain de cire claire tremble, sous le souffle arrêté.</t>
+          <t>Le portrait a failli garder le cheveu. J'ai soufflé, moi. Puis on a accroché, après l'air. On descend, la rampe est libre. Le cadre reste droit, contre le mur. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le grain de cire claire tremble, sous le souffle arrêté.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli garder le cheveu. J'ai soufflé, moi. Puis on a accroché, après l'air. On descend, la rampe est libre. Le cadre reste droit, contre le mur. Son souffle a passé, d'abord. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; tremble, sous le souffle arrêté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli garder le cheveu. J'ai soufflé, moi. Puis on a accroché, après l'air. On descend, la rampe est libre. Le cadre reste droit, contre le mur. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; tremble, sous le souffle arrêté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli garder le cheveu. J'ai soufflé, moi. Puis on a accroché, après l'air. On descend, la rampe est libre. Le cadre reste droit, contre le mur. Son souffle a passé, d'abord. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; tremble, sous le souffle arrêté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli garder le cheveu. J'ai soufflé, moi. Puis on a accroché, après l'air. On descend, la rampe est libre. Le cadre reste droit, contre le mur. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; tremble, sous le souffle arrêté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5332,6 +5345,7 @@
 papa|On descend, la rampe est libre.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|Son souffle a passé, d'abord.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire tremble, sous le souffle arrêté.</t>
         </is>
       </c>
@@ -5557,17 +5571,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?</t>
+          <t>La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -5727,6 +5741,7 @@
         <is>
           <t>narrateur|La manche cache le clou, trop longue.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 maman|Tu vois le grain, toi ?
 papa|La manche, le bouton, ou le clou ?</t>
         </is>
@@ -5755,17 +5770,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Ta manche, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, à son rythme. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le cadre, sans presser. Tu as laissé sa manche finir. On accroche, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le portrait monte, la manche haute.</t>
+          <t>Ta manche, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, à son rythme. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le cadre, sans presser. Tu as laissé sa manche finir. On accroche, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le portrait monte, la manche haute.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ta &lt;emphasis level="moderate"&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, à son rythme. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le cadre, sans presser. Tu as laissé sa manche finir. On accroche, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le portrait monte, la manche haute.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ta &lt;emphasis level="moderate"&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, à son rythme. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le cadre, sans presser. Tu as laissé sa manche finir. On accroche, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le portrait monte, la manche haute.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Ta &lt;emphasis&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, à son rythme. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le cadre, sans presser. Tu as laissé sa manche finir. On accroche, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le portrait monte, la manche haute. [pause]</t>
+          <t>Ta &lt;emphasis&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, à son rythme. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le cadre, sans presser. Tu as laissé sa manche finir. On accroche, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le portrait monte, la manche haute. [pause]</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -5909,6 +5924,7 @@
 enfant-f|On accroche, maintenant.
 maman|Le manteau attend, un peu.
 narrateur|Personne n'a tiré le bras.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, la manche haute.</t>
         </is>
       </c>
@@ -5941,17 +5957,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le cadre reste droit, contre le mur. Sa manche a fini, à son rythme. Le grain de cire claire sort de la manche, au clou.</t>
+          <t>Le portrait a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le cadre reste droit, contre le mur. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le grain de cire claire sort de la manche, au clou.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le cadre reste droit, contre le mur. Sa manche a fini, à son rythme. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sort de la manche, au clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le cadre reste droit, contre le mur. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sort de la manche, au clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le cadre reste droit, contre le mur. Sa manche a fini, à son rythme. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sort de la manche, au clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le cadre reste droit, contre le mur. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sort de la manche, au clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6095,6 +6111,7 @@
 papa|On descend, le manteau sous le bras.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|Sa manche a fini, à son rythme.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire sort de la manche, au clou.</t>
         </is>
       </c>
@@ -6127,17 +6144,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Le bouton, d'abord. Elle tend le poignet, trop vite. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le portrait monte, le poignet net.</t>
+          <t>Le bouton, d'abord. Elle tend le poignet, trop vite. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le portrait monte, le poignet net.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, trop vite. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le portrait monte, le poignet net.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, trop vite. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le portrait monte, le poignet net.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, trop vite. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le portrait monte, le poignet net. [pause]</t>
+          <t>Le &lt;emphasis&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, trop vite. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le portrait monte, le poignet net. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6281,6 +6298,7 @@
 enfant-f|Le clou est libre.
 maman|Le manteau peut attendre un bouton.
 narrateur|Personne n'a fermé à sa place.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, le poignet net.</t>
         </is>
       </c>
@@ -6313,17 +6331,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli attendre le bouton. C'est fermé, maintenant. Puis on a accroché, le poignet net. On descend, un bouton brille. Le cadre reste droit, contre le mur. Ses doigts ont boutonné, lentement. Le grain de cire claire brille près du bouton.</t>
+          <t>Le portrait a failli attendre le bouton. C'est fermé, maintenant. Puis on a accroché, le poignet net. On descend, un bouton brille. Le cadre reste droit, contre le mur. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le grain de cire claire brille près du bouton.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli attendre le bouton. C'est fermé, maintenant. Puis on a accroché, le poignet net. On descend, un bouton brille. Le cadre reste droit, contre le mur. Ses doigts ont boutonné, lentement. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille près du bouton.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli attendre le bouton. C'est fermé, maintenant. Puis on a accroché, le poignet net. On descend, un bouton brille. Le cadre reste droit, contre le mur. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille près du bouton.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli attendre le bouton. C'est fermé, maintenant. Puis on a accroché, le poignet net. On descend, un bouton brille. Le cadre reste droit, contre le mur. Ses doigts ont boutonné, lentement. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille près du bouton.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli attendre le bouton. C'est fermé, maintenant. Puis on a accroché, le poignet net. On descend, un bouton brille. Le cadre reste droit, contre le mur. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille près du bouton.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6467,6 +6485,7 @@
 papa|On descend, un bouton brille.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|Ses doigts ont boutonné, lentement.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire brille près du bouton.</t>
         </is>
       </c>
@@ -6499,17 +6518,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le clou, on le cherche. Elle regarde le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lève le cadre, vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le portrait monte, sur le grain.</t>
+          <t>Le clou, on le cherche. Elle regarde le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lève le cadre, vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le portrait monte, sur le grain.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;clou&lt;/emphasis&gt;, on le cherche. Elle regarde le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lève le cadre, vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le portrait monte, sur le grain.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;clou&lt;/emphasis&gt;, on le cherche. Elle regarde le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lève le cadre, vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le portrait monte, sur le grain.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;clou&lt;/emphasis&gt;, on le cherche. Elle regarde le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lève le cadre, vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le portrait monte, sur le grain. [pause]</t>
+          <t>Le &lt;emphasis&gt;clou&lt;/emphasis&gt;, on le cherche. Elle regarde le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lève le cadre, vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le portrait monte, sur le grain. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6653,6 +6672,7 @@
 enfant-f|On accroche, sur le grain.
 maman|Le manteau a attendu le clou.
 narrateur|Personne n'a nommé le chemin.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le portrait monte, sur le grain.</t>
         </is>
       </c>
@@ -6685,17 +6705,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Le portrait a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le cadre reste droit, contre le mur. Son doigt a trouvé le clou. Le grain de cire claire montre le clou, enfin.</t>
+          <t>Le portrait a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le cadre reste droit, contre le mur. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le grain de cire claire montre le clou, enfin.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le cadre reste droit, contre le mur. Son doigt a trouvé le clou. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; montre le clou, enfin.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le portrait a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le cadre reste droit, contre le mur. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; montre le clou, enfin.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le cadre reste droit, contre le mur. Son doigt a trouvé le clou. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; montre le clou, enfin.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le portrait a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le cadre reste droit, contre le mur. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; montre le clou, enfin.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -6839,6 +6859,7 @@
 papa|On descend, la porte des chambres se tait.
 maman|Le cadre reste droit, contre le mur.
 enfant-f|Son doigt a trouvé le clou.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire montre le clou, enfin.</t>
         </is>
       </c>
@@ -7825,17 +7846,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?</t>
+          <t>Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -7995,6 +8016,7 @@
         <is>
           <t>narrateur|Le soleil cache le clou, trop blanc.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 maman|Tu vois le grain, toi ?
 papa|Les lunettes, Mila tient, ou le nuage ?</t>
         </is>
@@ -8023,17 +8045,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Tes lunettes, d'abord. Elle baisse les lunettes, le chiffon à la main. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au fil. La photo, moi. Mila frotte le verre, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment frotter. Le verre luit, puis le portrait monte.</t>
+          <t>Tes lunettes, d'abord. Elle baisse les lunettes, le chiffon à la main. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au fil. La photo, moi. Mila frotte le verre, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment frotter. Ça a failli ne pas tenir. Le verre luit, puis le portrait monte.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tes &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, le chiffon à la main. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au fil. La photo, moi. Mila frotte le verre, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment frotter. Le verre luit, puis le portrait monte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tes &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, le chiffon à la main. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au fil. La photo, moi. Mila frotte le verre, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment frotter. Ça a failli ne pas tenir. Le verre luit, puis le portrait monte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Tes &lt;emphasis&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, le chiffon à la main. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au fil. La photo, moi. Mila frotte le verre, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment frotter. Le verre luit, puis le portrait monte. [pause]</t>
+          <t>Tes &lt;emphasis&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, le chiffon à la main. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au fil. La photo, moi. Mila frotte le verre, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment frotter. Ça a failli ne pas tenir. Le verre luit, puis le portrait monte. [pause]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -8177,6 +8199,7 @@
 enfant-f|Oui, le grain est dessus.
 maman|Vous l'avez, toutes les deux.
 narrateur|Personne n'a dit comment frotter.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le verre luit, puis le portrait monte.</t>
         </is>
       </c>
@@ -8209,17 +8232,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Le verre a failli rester trop blanc. Les lunettes ont laissé le chiffon. J'ai vu la photo, d'abord. On descend, ça sent la cire. Le chiffon reste plié, près du cadre. Mila a frotté, à sa façon. Un grain de cire claire reste au fil du chiffon.</t>
+          <t>Le verre a failli rester trop blanc. Les lunettes ont laissé le chiffon. J'ai vu la photo, d'abord. On descend, ça sent la cire. Le chiffon reste plié, près du cadre. Mila a frotté, à sa façon. Le petit toc du début s'est tu. Un grain de cire claire reste au fil du chiffon.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le verre a failli rester trop blanc. Les lunettes ont laissé le chiffon. J'ai vu la photo, d'abord. On descend, ça sent la cire. Le chiffon reste plié, près du cadre. Mila a frotté, à sa façon. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; reste au fil du chiffon.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le verre a failli rester trop blanc. Les lunettes ont laissé le chiffon. J'ai vu la photo, d'abord. On descend, ça sent la cire. Le chiffon reste plié, près du cadre. Mila a frotté, à sa façon. Le petit toc du début s'est tu. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; reste au fil du chiffon.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le verre a failli rester trop blanc. Les lunettes ont laissé le chiffon. J'ai vu la photo, d'abord. On descend, ça sent la cire. Le chiffon reste plié, près du cadre. Mila a frotté, à sa façon. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; reste au fil du chiffon.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le verre a failli rester trop blanc. Les lunettes ont laissé le chiffon. J'ai vu la photo, d'abord. On descend, ça sent la cire. Le chiffon reste plié, près du cadre. Mila a frotté, à sa façon. Le petit toc du début s'est tu. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; reste au fil du chiffon.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8363,6 +8386,7 @@
 papa|On descend, ça sent la cire.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|Mila a frotté, à sa façon.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Un grain de cire claire reste au fil du chiffon.</t>
         </is>
       </c>
@@ -8395,17 +8419,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le chiffon, Mila. Elle lâche un peu, sans l'arracher. Mila frotte à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au fil. Là, je vois. Tu as laissé ses mains finir. On lustre, après. Le clou attend, un peu. Personne n'a crié la réponse. Le verre luit, porté par Mila.</t>
+          <t>Tu tiens le chiffon, Mila. Elle lâche un peu, sans l'arracher. Mila frotte à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au fil. Là, je vois. Tu as laissé ses mains finir. On lustre, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le verre luit, porté par Mila.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu tiens le chiffon, &lt;emphasis level="moderate"&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans l'arracher. Mila frotte à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au fil. Là, je vois. Tu as laissé ses mains finir. On lustre, après. Le clou attend, un peu. Personne n'a crié la réponse. Le verre luit, porté par Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu tiens le chiffon, &lt;emphasis level="moderate"&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans l'arracher. Mila frotte à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au fil. Là, je vois. Tu as laissé ses mains finir. On lustre, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le verre luit, porté par Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le chiffon, &lt;emphasis&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans l'arracher. Mila frotte à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au fil. Là, je vois. Tu as laissé ses mains finir. On lustre, après. Le clou attend, un peu. Personne n'a crié la réponse. Le verre luit, porté par Mila. [pause]</t>
+          <t>Tu tiens le chiffon, &lt;emphasis&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans l'arracher. Mila frotte à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au fil. Là, je vois. Tu as laissé ses mains finir. On lustre, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le verre luit, porté par Mila. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8549,6 +8573,7 @@
 enfant-f|On lustre, après.
 maman|Le clou attend, un peu.
 narrateur|Personne n'a crié la réponse.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le verre luit, porté par Mila.</t>
         </is>
       </c>
@@ -8581,17 +8606,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Le verre a failli rester trop bas. J'ai tenu le chiffon, moi. Puis on a lustré, ensemble. On descend, les mains un peu grasses. Le chiffon reste plié, près du cadre. Ses mains ont choisi la hauteur. Le grain de cire claire brille au fil, bas.</t>
+          <t>Le verre a failli rester trop bas. J'ai tenu le chiffon, moi. Puis on a lustré, ensemble. On descend, les mains un peu grasses. Le chiffon reste plié, près du cadre. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le grain de cire claire brille au fil, bas.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le verre a failli rester trop bas. J'ai tenu le chiffon, moi. Puis on a lustré, ensemble. On descend, les mains un peu grasses. Le chiffon reste plié, près du cadre. Ses mains ont choisi la hauteur. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille au fil, bas.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le verre a failli rester trop bas. J'ai tenu le chiffon, moi. Puis on a lustré, ensemble. On descend, les mains un peu grasses. Le chiffon reste plié, près du cadre. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille au fil, bas.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le verre a failli rester trop bas. J'ai tenu le chiffon, moi. Puis on a lustré, ensemble. On descend, les mains un peu grasses. Le chiffon reste plié, près du cadre. Ses mains ont choisi la hauteur. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille au fil, bas.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le verre a failli rester trop bas. J'ai tenu le chiffon, moi. Puis on a lustré, ensemble. On descend, les mains un peu grasses. Le chiffon reste plié, près du cadre. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille au fil, bas.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8735,6 +8760,7 @@
 papa|On descend, les mains un peu grasses.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|Ses mains ont choisi la hauteur.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire brille au fil, bas.</t>
         </is>
       </c>
@@ -8767,17 +8793,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le nuage, d'abord. Elle attend, le chiffon contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila frotte le verre, à son heure. Le soleil a laissé le clou. On lustre, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le verre luit, sans le blanc.</t>
+          <t>Le nuage, d'abord. Elle attend, le chiffon contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila frotte le verre, à son heure. Le soleil a laissé le clou. On lustre, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le verre luit, sans le blanc.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le chiffon contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila frotte le verre, à son heure. Le soleil a laissé le clou. On lustre, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le verre luit, sans le blanc.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le chiffon contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila frotte le verre, à son heure. Le soleil a laissé le clou. On lustre, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le verre luit, sans le blanc.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le chiffon contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila frotte le verre, à son heure. Le soleil a laissé le clou. On lustre, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le verre luit, sans le blanc. [pause]</t>
+          <t>Le &lt;emphasis&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le chiffon contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila frotte le verre, à son heure. Le soleil a laissé le clou. On lustre, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le verre luit, sans le blanc. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8921,6 +8947,7 @@
 enfant-f|On lustre, lentement.
 maman|Vous avez attendu ensemble.
 narrateur|Personne n'a pressé le nuage.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le verre luit, sans le blanc.</t>
         </is>
       </c>
@@ -8953,17 +8980,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Le verre a failli attendre le soleil. Le nuage a passé. Puis on a lustré, sans le blanc. On descend, la fenêtre ronde est grise. Le chiffon reste plié, près du cadre. On a attendu le nuage, toutes les deux. Le grain de cire claire sèche au fil, après le nuage.</t>
+          <t>Le verre a failli attendre le soleil. Le nuage a passé. Puis on a lustré, sans le blanc. On descend, la fenêtre ronde est grise. Le chiffon reste plié, près du cadre. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le grain de cire claire sèche au fil, après le nuage.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le verre a failli attendre le soleil. Le nuage a passé. Puis on a lustré, sans le blanc. On descend, la fenêtre ronde est grise. Le chiffon reste plié, près du cadre. On a attendu le nuage, toutes les deux. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sèche au fil, après le nuage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le verre a failli attendre le soleil. Le nuage a passé. Puis on a lustré, sans le blanc. On descend, la fenêtre ronde est grise. Le chiffon reste plié, près du cadre. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sèche au fil, après le nuage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le verre a failli attendre le soleil. Le nuage a passé. Puis on a lustré, sans le blanc. On descend, la fenêtre ronde est grise. Le chiffon reste plié, près du cadre. On a attendu le nuage, toutes les deux. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sèche au fil, après le nuage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le verre a failli attendre le soleil. Le nuage a passé. Puis on a lustré, sans le blanc. On descend, la fenêtre ronde est grise. Le chiffon reste plié, près du cadre. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sèche au fil, après le nuage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9107,6 +9134,7 @@
 papa|On descend, la fenêtre ronde est grise.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|On a attendu le nuage, toutes les deux.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire sèche au fil, après le nuage.</t>
         </is>
       </c>
@@ -9332,17 +9360,17 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?</t>
+          <t>Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -9502,6 +9530,7 @@
         <is>
           <t>narrateur|Les cheveux gênent, contre la rampe.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 papa|Tu vois le grain, toi ?
 maman|Le nœud, l'oreille, ou Mila souffle ?</t>
         </is>
@@ -9530,17 +9559,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Un nœud, dans tes cheveux. Elle tend un élastique, le chiffon au poignet. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au fil. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le chiffon luit, le nœud tenu.</t>
+          <t>Un nœud, dans tes cheveux. Elle tend un élastique, le chiffon au poignet. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au fil. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le chiffon luit, le nœud tenu.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un &lt;emphasis level="moderate"&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, le chiffon au poignet. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au fil. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le chiffon luit, le nœud tenu.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un &lt;emphasis level="moderate"&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, le chiffon au poignet. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au fil. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le chiffon luit, le nœud tenu.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Un &lt;emphasis&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, le chiffon au poignet. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au fil. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le chiffon luit, le nœud tenu. [pause]</t>
+          <t>Un &lt;emphasis&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, le chiffon au poignet. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au fil. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le chiffon luit, le nœud tenu. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9684,6 +9713,7 @@
 enfant-f|La bouche est libre.
 maman|La rampe peut attendre.
 narrateur|Personne n'a tiré les cheveux.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le chiffon luit, le nœud tenu.</t>
         </is>
       </c>
@@ -9716,17 +9746,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a lustré, la bouche libre. On descend, la rampe est lisse. Le chiffon reste plié, près du cadre. Ses doigts ont noué, lentement. Un grain de cire claire colle au nœud du chiffon.</t>
+          <t>Le chiffon a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a lustré, la bouche libre. On descend, la rampe est lisse. Le chiffon reste plié, près du cadre. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un grain de cire claire colle au nœud du chiffon.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a lustré, la bouche libre. On descend, la rampe est lisse. Le chiffon reste plié, près du cadre. Ses doigts ont noué, lentement. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud du chiffon.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a lustré, la bouche libre. On descend, la rampe est lisse. Le chiffon reste plié, près du cadre. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud du chiffon.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a lustré, la bouche libre. On descend, la rampe est lisse. Le chiffon reste plié, près du cadre. Ses doigts ont noué, lentement. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud du chiffon.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a lustré, la bouche libre. On descend, la rampe est lisse. Le chiffon reste plié, près du cadre. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud du chiffon.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9870,6 +9900,7 @@
 papa|On descend, la rampe est lisse.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|Ses doigts ont noué, lentement.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Un grain de cire claire colle au nœud du chiffon.</t>
         </is>
       </c>
@@ -9902,17 +9933,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>J'écoute, près de ton oreille. Elle se tait, le chiffon contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au fil. Victorina baisse le chiffon, vers l'oreille. Tu as entendu, sans parler dessus. On lustre, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le verre luit, à voix basse.</t>
+          <t>J'écoute, près de ton oreille. Elle se tait, le chiffon contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au fil. Victorina baisse le chiffon, vers l'oreille. Tu as entendu, sans parler dessus. On lustre, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le verre luit, à voix basse.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;J'écoute, près de ton &lt;emphasis level="moderate"&gt;oreille&lt;/emphasis&gt;. Elle se tait, le chiffon contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au fil. Victorina baisse le chiffon, vers l'oreille. Tu as entendu, sans parler dessus. On lustre, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le verre luit, à voix basse.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;J'écoute, près de ton &lt;emphasis level="moderate"&gt;oreille&lt;/emphasis&gt;. Elle se tait, le chiffon contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au fil. Victorina baisse le chiffon, vers l'oreille. Tu as entendu, sans parler dessus. On lustre, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le verre luit, à voix basse.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>J'écoute, près de ton &lt;emphasis&gt;oreille&lt;/emphasis&gt;. Elle se tait, le chiffon contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au fil. Victorina baisse le chiffon, vers l'oreille. Tu as entendu, sans parler dessus. On lustre, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le verre luit, à voix basse. [pause]</t>
+          <t>J'écoute, près de ton &lt;emphasis&gt;oreille&lt;/emphasis&gt;. Elle se tait, le chiffon contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au fil. Victorina baisse le chiffon, vers l'oreille. Tu as entendu, sans parler dessus. On lustre, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le verre luit, à voix basse. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -10056,6 +10087,7 @@
 enfant-f|On lustre, plus bas.
 maman|Sa voix a choisi la hauteur.
 narrateur|Personne n'a donné le plan.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le verre luit, à voix basse.</t>
         </is>
       </c>
@@ -10088,17 +10120,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le chiffon reste plié, près du cadre. Sa voix a choisi, toute basse. Le grain de cire claire attend au fil, près de l'oreille.</t>
+          <t>Le chiffon a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le chiffon reste plié, près du cadre. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le grain de cire claire attend au fil, près de l'oreille.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le chiffon reste plié, près du cadre. Sa voix a choisi, toute basse. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; attend au fil, près de l'oreille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le chiffon reste plié, près du cadre. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; attend au fil, près de l'oreille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le chiffon reste plié, près du cadre. Sa voix a choisi, toute basse. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; attend au fil, près de l'oreille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le chiffon reste plié, près du cadre. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; attend au fil, près de l'oreille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10242,6 +10274,7 @@
 papa|On descend, sans crier.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|Sa voix a choisi, toute basse.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire attend au fil, près de l'oreille.</t>
         </is>
       </c>
@@ -10274,17 +10307,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Tu souffles, Mila. Elle attend, le chiffon plié. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina frotte le verre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le verre luit, après son air.</t>
+          <t>Tu souffles, Mila. Elle attend, le chiffon plié. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina frotte le verre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le verre luit, après son air.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu &lt;emphasis level="moderate"&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, le chiffon plié. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina frotte le verre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le verre luit, après son air.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu &lt;emphasis level="moderate"&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, le chiffon plié. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina frotte le verre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le verre luit, après son air.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Tu &lt;emphasis&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, le chiffon plié. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina frotte le verre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le verre luit, après son air. [pause]</t>
+          <t>Tu &lt;emphasis&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, le chiffon plié. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina frotte le verre, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le verre luit, après son air. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10428,6 +10461,7 @@
 enfant-f|La bouche est libre.
 maman|La rampe n'a plus pris les cheveux.
 narrateur|Personne n'a soufflé à sa place.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le verre luit, après son air.</t>
         </is>
       </c>
@@ -10460,17 +10494,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon a failli garder le cheveu. J'ai soufflé, moi. Puis on a lustré, après l'air. On descend, la rampe est libre. Le chiffon reste plié, près du cadre. Son souffle a passé, d'abord. Le grain de cire claire tremble au fil, sous l'air arrêté.</t>
+          <t>Le chiffon a failli garder le cheveu. J'ai soufflé, moi. Puis on a lustré, après l'air. On descend, la rampe est libre. Le chiffon reste plié, près du cadre. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le grain de cire claire tremble au fil, sous l'air arrêté.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli garder le cheveu. J'ai soufflé, moi. Puis on a lustré, après l'air. On descend, la rampe est libre. Le chiffon reste plié, près du cadre. Son souffle a passé, d'abord. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; tremble au fil, sous l'air arrêté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli garder le cheveu. J'ai soufflé, moi. Puis on a lustré, après l'air. On descend, la rampe est libre. Le chiffon reste plié, près du cadre. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; tremble au fil, sous l'air arrêté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli garder le cheveu. J'ai soufflé, moi. Puis on a lustré, après l'air. On descend, la rampe est libre. Le chiffon reste plié, près du cadre. Son souffle a passé, d'abord. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; tremble au fil, sous l'air arrêté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli garder le cheveu. J'ai soufflé, moi. Puis on a lustré, après l'air. On descend, la rampe est libre. Le chiffon reste plié, près du cadre. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; tremble au fil, sous l'air arrêté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10614,6 +10648,7 @@
 papa|On descend, la rampe est libre.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|Son souffle a passé, d'abord.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire tremble au fil, sous l'air arrêté.</t>
         </is>
       </c>
@@ -10839,17 +10874,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?</t>
+          <t>La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -11009,6 +11044,7 @@
         <is>
           <t>narrateur|La manche cache le clou, trop longue.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 maman|Tu vois le grain, toi ?
 papa|La manche, le bouton, ou le clou ?</t>
         </is>
@@ -11037,17 +11073,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Ta manche, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, le chiffon dedans. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tend le chiffon, sans presser. Tu as laissé sa manche finir. On lustre, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le verre luit, la manche haute.</t>
+          <t>Ta manche, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, le chiffon dedans. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tend le chiffon, sans presser. Tu as laissé sa manche finir. On lustre, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le verre luit, la manche haute.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ta &lt;emphasis level="moderate"&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, le chiffon dedans. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tend le chiffon, sans presser. Tu as laissé sa manche finir. On lustre, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le verre luit, la manche haute.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ta &lt;emphasis level="moderate"&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, le chiffon dedans. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tend le chiffon, sans presser. Tu as laissé sa manche finir. On lustre, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le verre luit, la manche haute.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Ta &lt;emphasis&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, le chiffon dedans. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tend le chiffon, sans presser. Tu as laissé sa manche finir. On lustre, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le verre luit, la manche haute. [pause]</t>
+          <t>Ta &lt;emphasis&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, le chiffon dedans. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tend le chiffon, sans presser. Tu as laissé sa manche finir. On lustre, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le verre luit, la manche haute. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11191,6 +11227,7 @@
 enfant-f|On lustre, maintenant.
 maman|Le manteau attend, un peu.
 narrateur|Personne n'a tiré le bras.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le verre luit, la manche haute.</t>
         </is>
       </c>
@@ -11223,17 +11260,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le chiffon reste plié, près du cadre. Sa manche a fini, à son rythme. Le grain de cire claire sort du chiffon, au clou.</t>
+          <t>Le chiffon a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le chiffon reste plié, près du cadre. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le grain de cire claire sort du chiffon, au clou.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le chiffon reste plié, près du cadre. Sa manche a fini, à son rythme. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sort du chiffon, au clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le chiffon reste plié, près du cadre. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sort du chiffon, au clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le chiffon reste plié, près du cadre. Sa manche a fini, à son rythme. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sort du chiffon, au clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le chiffon reste plié, près du cadre. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sort du chiffon, au clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11377,6 +11414,7 @@
 papa|On descend, le manteau sous le bras.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|Sa manche a fini, à son rythme.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire sort du chiffon, au clou.</t>
         </is>
       </c>
@@ -11409,17 +11447,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Le bouton, d'abord. Elle tend le poignet, le chiffon collé. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le verre luit, le poignet net.</t>
+          <t>Le bouton, d'abord. Elle tend le poignet, le chiffon collé. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le verre luit, le poignet net.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, le chiffon collé. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le verre luit, le poignet net.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, le chiffon collé. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le verre luit, le poignet net.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, le chiffon collé. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le verre luit, le poignet net. [pause]</t>
+          <t>Le &lt;emphasis&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, le chiffon collé. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le verre luit, le poignet net. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11563,6 +11601,7 @@
 enfant-f|Le clou est libre.
 maman|Le manteau peut attendre un bouton.
 narrateur|Personne n'a fermé à sa place.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le verre luit, le poignet net.</t>
         </is>
       </c>
@@ -11595,17 +11634,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon a failli attendre le bouton. C'est fermé, maintenant. Puis on a lustré, le poignet net. On descend, un bouton brille. Le chiffon reste plié, près du cadre. Ses doigts ont boutonné, lentement. Le grain de cire claire brille au fil, près du bouton.</t>
+          <t>Le chiffon a failli attendre le bouton. C'est fermé, maintenant. Puis on a lustré, le poignet net. On descend, un bouton brille. Le chiffon reste plié, près du cadre. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le grain de cire claire brille au fil, près du bouton.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli attendre le bouton. C'est fermé, maintenant. Puis on a lustré, le poignet net. On descend, un bouton brille. Le chiffon reste plié, près du cadre. Ses doigts ont boutonné, lentement. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille au fil, près du bouton.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli attendre le bouton. C'est fermé, maintenant. Puis on a lustré, le poignet net. On descend, un bouton brille. Le chiffon reste plié, près du cadre. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille au fil, près du bouton.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli attendre le bouton. C'est fermé, maintenant. Puis on a lustré, le poignet net. On descend, un bouton brille. Le chiffon reste plié, près du cadre. Ses doigts ont boutonné, lentement. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille au fil, près du bouton.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli attendre le bouton. C'est fermé, maintenant. Puis on a lustré, le poignet net. On descend, un bouton brille. Le chiffon reste plié, près du cadre. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille au fil, près du bouton.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11749,6 +11788,7 @@
 papa|On descend, un bouton brille.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|Ses doigts ont boutonné, lentement.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire brille au fil, près du bouton.</t>
         </is>
       </c>
@@ -11781,17 +11821,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Le clou, on le cherche. Elle frotte le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lustre vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le verre luit, sur le grain.</t>
+          <t>Le clou, on le cherche. Elle frotte le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lustre vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le verre luit, sur le grain.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;clou&lt;/emphasis&gt;, on le cherche. Elle frotte le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lustre vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le verre luit, sur le grain.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;clou&lt;/emphasis&gt;, on le cherche. Elle frotte le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lustre vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le verre luit, sur le grain.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;clou&lt;/emphasis&gt;, on le cherche. Elle frotte le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lustre vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le verre luit, sur le grain. [pause]</t>
+          <t>Le &lt;emphasis&gt;clou&lt;/emphasis&gt;, on le cherche. Elle frotte le bois, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina lustre vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le verre luit, sur le grain. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11935,6 +11975,7 @@
 enfant-f|On accroche, sur le grain.
 maman|Le manteau a attendu le clou.
 narrateur|Personne n'a nommé le chemin.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le verre luit, sur le grain.</t>
         </is>
       </c>
@@ -11967,17 +12008,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le chiffon reste plié, près du cadre. Son doigt a trouvé le clou. Le grain de cire claire luit au fil, sur le clou.</t>
+          <t>Le chiffon a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le chiffon reste plié, près du cadre. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le grain de cire claire luit au fil, sur le clou.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le chiffon reste plié, près du cadre. Son doigt a trouvé le clou. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; luit au fil, sur le clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le chiffon a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le chiffon reste plié, près du cadre. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; luit au fil, sur le clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le chiffon reste plié, près du cadre. Son doigt a trouvé le clou. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; luit au fil, sur le clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le chiffon a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le chiffon reste plié, près du cadre. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; luit au fil, sur le clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12121,6 +12162,7 @@
 papa|On descend, la porte des chambres se tait.
 maman|Le chiffon reste plié, près du cadre.
 enfant-f|Son doigt a trouvé le clou.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire luit au fil, sur le clou.</t>
         </is>
       </c>
@@ -13107,17 +13149,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?</t>
+          <t>Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Le soleil cache le clou, trop blanc. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Les lunettes, Mila tient, ou le nuage ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -13277,6 +13319,7 @@
         <is>
           <t>narrateur|Le soleil cache le clou, trop blanc.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 maman|Tu vois le grain, toi ?
 papa|Les lunettes, Mila tient, ou le nuage ?</t>
         </is>
@@ -13305,17 +13348,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Tes lunettes, d'abord. Elle baisse les lunettes, près du tabouret. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au pied. La photo, moi. Mila pose un pied, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment monter. Le tabouret tient, puis le portrait monte.</t>
+          <t>Tes lunettes, d'abord. Elle baisse les lunettes, près du tabouret. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au pied. La photo, moi. Mila pose un pied, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment monter. Ça a failli ne pas tenir. Le tabouret tient, puis le portrait monte.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tes &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, près du tabouret. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au pied. La photo, moi. Mila pose un pied, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment monter. Le tabouret tient, puis le portrait monte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tes &lt;emphasis level="moderate"&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, près du tabouret. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au pied. La photo, moi. Mila pose un pied, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment monter. Ça a failli ne pas tenir. Le tabouret tient, puis le portrait monte.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Tes &lt;emphasis&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, près du tabouret. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au pied. La photo, moi. Mila pose un pied, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment monter. Le tabouret tient, puis le portrait monte. [pause]</t>
+          <t>Tes &lt;emphasis&gt;lunettes&lt;/emphasis&gt;, d'abord. Elle baisse les lunettes, près du tabouret. Puis elle s'arrête, et elle écoute le palier. Le grain de cire claire reparaît, au pied. La photo, moi. Mila pose un pied, plus lentement. Tu vois le clou, maintenant ? Oui, le grain est dessus. Vous l'avez, toutes les deux. Personne n'a dit comment monter. Ça a failli ne pas tenir. Le tabouret tient, puis le portrait monte. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13459,6 +13502,7 @@
 enfant-f|Oui, le grain est dessus.
 maman|Vous l'avez, toutes les deux.
 narrateur|Personne n'a dit comment monter.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret tient, puis le portrait monte.</t>
         </is>
       </c>
@@ -13491,17 +13535,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli rester trop blanc. Les lunettes ont laissé le bois. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le tabouret reste bas, près du mur. Mila a posé le pied, à sa façon. Un grain de cire claire reste au pied du tabouret.</t>
+          <t>Le tabouret a failli rester trop blanc. Les lunettes ont laissé le bois. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le tabouret reste bas, près du mur. Mila a posé le pied, à sa façon. Le petit toc du début s'est tu. Un grain de cire claire reste au pied du tabouret.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli rester trop blanc. Les lunettes ont laissé le bois. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le tabouret reste bas, près du mur. Mila a posé le pied, à sa façon. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; reste au pied du tabouret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli rester trop blanc. Les lunettes ont laissé le bois. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le tabouret reste bas, près du mur. Mila a posé le pied, à sa façon. Le petit toc du début s'est tu. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; reste au pied du tabouret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli rester trop blanc. Les lunettes ont laissé le bois. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le tabouret reste bas, près du mur. Mila a posé le pied, à sa façon. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; reste au pied du tabouret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli rester trop blanc. Les lunettes ont laissé le bois. J'ai vu la photo, d'abord. On descend, le palier sent la cire. Le tabouret reste bas, près du mur. Mila a posé le pied, à sa façon. Le petit toc du début s'est tu. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; reste au pied du tabouret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13645,6 +13689,7 @@
 papa|On descend, le palier sent la cire.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|Mila a posé le pied, à sa façon.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Un grain de cire claire reste au pied du tabouret.</t>
         </is>
       </c>
@@ -13677,17 +13722,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le tabouret, Mila. Elle lâche un peu, sans le tirer. Mila le pousse à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au pied. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Le tabouret avance, poussé par Mila.</t>
+          <t>Tu tiens le tabouret, Mila. Elle lâche un peu, sans le tirer. Mila le pousse à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au pied. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le tabouret avance, poussé par Mila.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu tiens le tabouret, &lt;emphasis level="moderate"&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans le tirer. Mila le pousse à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au pied. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Le tabouret avance, poussé par Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu tiens le tabouret, &lt;emphasis level="moderate"&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans le tirer. Mila le pousse à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au pied. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le tabouret avance, poussé par Mila.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Tu tiens le tabouret, &lt;emphasis&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans le tirer. Mila le pousse à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au pied. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Le tabouret avance, poussé par Mila. [pause]</t>
+          <t>Tu tiens le tabouret, &lt;emphasis&gt;Mila&lt;/emphasis&gt;. Elle lâche un peu, sans le tirer. Mila le pousse à sa hauteur, trop basse. Victorina refuse de le lui prendre. Le grain de cire claire brille, au pied. Là, je vois. Tu as laissé ses mains finir. On monte, après. Le clou attend, un peu. Personne n'a crié la réponse. Ça a failli ne pas tenir. Le tabouret avance, poussé par Mila. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13831,6 +13876,7 @@
 enfant-f|On monte, après.
 maman|Le clou attend, un peu.
 narrateur|Personne n'a crié la réponse.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret avance, poussé par Mila.</t>
         </is>
       </c>
@@ -13863,17 +13909,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli rester trop bas. Je l'ai poussé, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le tabouret reste bas, près du mur. Ses mains ont choisi la hauteur. Le grain de cire claire brille au pied, bas.</t>
+          <t>Le tabouret a failli rester trop bas. Je l'ai poussé, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le tabouret reste bas, près du mur. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le grain de cire claire brille au pied, bas.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli rester trop bas. Je l'ai poussé, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le tabouret reste bas, près du mur. Ses mains ont choisi la hauteur. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille au pied, bas.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli rester trop bas. Je l'ai poussé, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le tabouret reste bas, près du mur. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille au pied, bas.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli rester trop bas. Je l'ai poussé, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le tabouret reste bas, près du mur. Ses mains ont choisi la hauteur. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille au pied, bas.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli rester trop bas. Je l'ai poussé, moi. Puis on a monté, ensemble. On descend, les mains un peu grasses. Le tabouret reste bas, près du mur. Ses mains ont choisi la hauteur. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille au pied, bas.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -14017,6 +14063,7 @@
 papa|On descend, les mains un peu grasses.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|Ses mains ont choisi la hauteur.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire brille au pied, bas.</t>
         </is>
       </c>
@@ -14049,17 +14096,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le nuage, d'abord. Elle attend, le tabouret contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila pose les deux pieds, à son heure. Le soleil a laissé le clou. On monte, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le tabouret tient, sans le blanc.</t>
+          <t>Le nuage, d'abord. Elle attend, le tabouret contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila pose les deux pieds, à son heure. Le soleil a laissé le clou. On monte, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le tabouret tient, sans le blanc.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le tabouret contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila pose les deux pieds, à son heure. Le soleil a laissé le clou. On monte, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le tabouret tient, sans le blanc.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le tabouret contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila pose les deux pieds, à son heure. Le soleil a laissé le clou. On monte, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le tabouret tient, sans le blanc.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le tabouret contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila pose les deux pieds, à son heure. Le soleil a laissé le clou. On monte, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Le tabouret tient, sans le blanc. [pause]</t>
+          <t>Le &lt;emphasis&gt;nuage&lt;/emphasis&gt;, d'abord. Elle attend, le tabouret contre elle. Un nuage passe sur la fenêtre ronde. Le grain de cire claire reparaît, net. Je vois, maintenant. Mila pose les deux pieds, à son heure. Le soleil a laissé le clou. On monte, lentement. Vous avez attendu ensemble. Personne n'a pressé le nuage. Ça a failli ne pas tenir. Le tabouret tient, sans le blanc. [pause]</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -14203,6 +14250,7 @@
 enfant-f|On monte, lentement.
 maman|Vous avez attendu ensemble.
 narrateur|Personne n'a pressé le nuage.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret tient, sans le blanc.</t>
         </is>
       </c>
@@ -14235,17 +14283,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli attendre le soleil. Le nuage a passé. Puis on a monté, sans le blanc. On descend, la fenêtre ronde est grise. Le tabouret reste bas, près du mur. On a attendu le nuage, toutes les deux. Le grain de cire claire sèche au pied, après le nuage.</t>
+          <t>Le tabouret a failli attendre le soleil. Le nuage a passé. Puis on a monté, sans le blanc. On descend, la fenêtre ronde est grise. Le tabouret reste bas, près du mur. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le grain de cire claire sèche au pied, après le nuage.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli attendre le soleil. Le nuage a passé. Puis on a monté, sans le blanc. On descend, la fenêtre ronde est grise. Le tabouret reste bas, près du mur. On a attendu le nuage, toutes les deux. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sèche au pied, après le nuage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli attendre le soleil. Le nuage a passé. Puis on a monté, sans le blanc. On descend, la fenêtre ronde est grise. Le tabouret reste bas, près du mur. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sèche au pied, après le nuage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli attendre le soleil. Le nuage a passé. Puis on a monté, sans le blanc. On descend, la fenêtre ronde est grise. Le tabouret reste bas, près du mur. On a attendu le nuage, toutes les deux. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sèche au pied, après le nuage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli attendre le soleil. Le nuage a passé. Puis on a monté, sans le blanc. On descend, la fenêtre ronde est grise. Le tabouret reste bas, près du mur. On a attendu le nuage, toutes les deux. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sèche au pied, après le nuage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -14389,6 +14437,7 @@
 papa|On descend, la fenêtre ronde est grise.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|On a attendu le nuage, toutes les deux.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire sèche au pied, après le nuage.</t>
         </is>
       </c>
@@ -14614,17 +14663,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?</t>
+          <t>Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;Les cheveux gênent, contre la rampe. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? Le nœud, l'oreille, ou Mila souffle ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -14784,6 +14833,7 @@
         <is>
           <t>narrateur|Les cheveux gênent, contre la rampe.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 papa|Tu vois le grain, toi ?
 maman|Le nœud, l'oreille, ou Mila souffle ?</t>
         </is>
@@ -14812,17 +14862,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Un nœud, dans tes cheveux. Elle tend un élastique, près du tabouret. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au pied. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le tabouret avance, le nœud tenu.</t>
+          <t>Un nœud, dans tes cheveux. Elle tend un élastique, près du tabouret. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au pied. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le tabouret avance, le nœud tenu.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un &lt;emphasis level="moderate"&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, près du tabouret. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au pied. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le tabouret avance, le nœud tenu.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un &lt;emphasis level="moderate"&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, près du tabouret. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au pied. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le tabouret avance, le nœud tenu.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Un &lt;emphasis&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, près du tabouret. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au pied. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Le tabouret avance, le nœud tenu. [pause]</t>
+          <t>Un &lt;emphasis&gt;nœud&lt;/emphasis&gt;, dans tes cheveux. Elle tend un élastique, près du tabouret. Puis elle attend que Mila noue. Mila fait le nœud, très lentement. Le grain de cire claire reste au pied. C'est fait. Tu as laissé ses doigts finir. La bouche est libre. La rampe peut attendre. Personne n'a tiré les cheveux. Ça a failli ne pas tenir. Le tabouret avance, le nœud tenu. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -14966,6 +15016,7 @@
 enfant-f|La bouche est libre.
 maman|La rampe peut attendre.
 narrateur|Personne n'a tiré les cheveux.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret avance, le nœud tenu.</t>
         </is>
       </c>
@@ -14998,17 +15049,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a monté, la bouche libre. On descend, la rampe est lisse. Le tabouret reste bas, près du mur. Ses doigts ont noué, lentement. Un grain de cire claire colle au nœud, près du bois.</t>
+          <t>Le tabouret a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a monté, la bouche libre. On descend, la rampe est lisse. Le tabouret reste bas, près du mur. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un grain de cire claire colle au nœud, près du bois.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a monté, la bouche libre. On descend, la rampe est lisse. Le tabouret reste bas, près du mur. Ses doigts ont noué, lentement. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud, près du bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a monté, la bouche libre. On descend, la rampe est lisse. Le tabouret reste bas, près du mur. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud, près du bois.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a monté, la bouche libre. On descend, la rampe est lisse. Le tabouret reste bas, près du mur. Ses doigts ont noué, lentement. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud, près du bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli rester dans les cheveux. Le nœud tient, tout petit. Puis on a monté, la bouche libre. On descend, la rampe est lisse. Le tabouret reste bas, près du mur. Ses doigts ont noué, lentement. Le petit toc du début s'est tu. Un &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; colle au nœud, près du bois.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15152,6 +15203,7 @@
 papa|On descend, la rampe est lisse.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|Ses doigts ont noué, lentement.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Un grain de cire claire colle au nœud, près du bois.</t>
         </is>
       </c>
@@ -15184,17 +15236,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>J'écoute, près de ton oreille. Elle se tait, le tabouret contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au pied. Victorina baisse le tabouret, vers l'oreille. Tu as entendu, sans parler dessus. On monte, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le tabouret avance, à voix basse.</t>
+          <t>J'écoute, près de ton oreille. Elle se tait, le tabouret contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au pied. Victorina baisse le tabouret, vers l'oreille. Tu as entendu, sans parler dessus. On monte, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le tabouret avance, à voix basse.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;J'écoute, près de ton &lt;emphasis level="moderate"&gt;oreille&lt;/emphasis&gt;. Elle se tait, le tabouret contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au pied. Victorina baisse le tabouret, vers l'oreille. Tu as entendu, sans parler dessus. On monte, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le tabouret avance, à voix basse.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;J'écoute, près de ton &lt;emphasis level="moderate"&gt;oreille&lt;/emphasis&gt;. Elle se tait, le tabouret contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au pied. Victorina baisse le tabouret, vers l'oreille. Tu as entendu, sans parler dessus. On monte, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le tabouret avance, à voix basse.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>J'écoute, près de ton &lt;emphasis&gt;oreille&lt;/emphasis&gt;. Elle se tait, le tabouret contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au pied. Victorina baisse le tabouret, vers l'oreille. Tu as entendu, sans parler dessus. On monte, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Le tabouret avance, à voix basse. [pause]</t>
+          <t>J'écoute, près de ton &lt;emphasis&gt;oreille&lt;/emphasis&gt;. Elle se tait, le tabouret contre la rampe. Mila souffle un tout petit mot. Pas trop haut. Le grain de cire claire attend, au pied. Victorina baisse le tabouret, vers l'oreille. Tu as entendu, sans parler dessus. On monte, plus bas. Sa voix a choisi la hauteur. Personne n'a donné le plan. Ça a failli ne pas tenir. Le tabouret avance, à voix basse. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15338,6 +15390,7 @@
 enfant-f|On monte, plus bas.
 maman|Sa voix a choisi la hauteur.
 narrateur|Personne n'a donné le plan.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret avance, à voix basse.</t>
         </is>
       </c>
@@ -15370,17 +15423,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le tabouret reste bas, près du mur. Sa voix a choisi, toute basse. Le grain de cire claire attend au pied, près de l'oreille.</t>
+          <t>Le tabouret a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le tabouret reste bas, près du mur. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le grain de cire claire attend au pied, près de l'oreille.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le tabouret reste bas, près du mur. Sa voix a choisi, toute basse. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; attend au pied, près de l'oreille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le tabouret reste bas, près du mur. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; attend au pied, près de l'oreille.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le tabouret reste bas, près du mur. Sa voix a choisi, toute basse. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; attend au pied, près de l'oreille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli parler trop fort. Pas trop haut. J'ai écouté, près de l'oreille. On descend, sans crier. Le tabouret reste bas, près du mur. Sa voix a choisi, toute basse. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; attend au pied, près de l'oreille.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -15524,6 +15577,7 @@
 papa|On descend, sans crier.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|Sa voix a choisi, toute basse.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire attend au pied, près de l'oreille.</t>
         </is>
       </c>
@@ -15556,17 +15610,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Tu souffles, Mila. Elle attend, les deux pieds à plat. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina pousse le tabouret, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le tabouret avance, après son air.</t>
+          <t>Tu souffles, Mila. Elle attend, les deux pieds à plat. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina pousse le tabouret, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le tabouret avance, après son air.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu &lt;emphasis level="moderate"&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, les deux pieds à plat. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina pousse le tabouret, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le tabouret avance, après son air.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tu &lt;emphasis level="moderate"&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, les deux pieds à plat. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina pousse le tabouret, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le tabouret avance, après son air.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Tu &lt;emphasis&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, les deux pieds à plat. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina pousse le tabouret, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Le tabouret avance, après son air. [pause]</t>
+          <t>Tu &lt;emphasis&gt;souffle&lt;/emphasis&gt;s, Mila. Elle attend, les deux pieds à plat. Mila souffle le cheveu, tout petit. Le grain de cire claire tremble, sous le souffle. Voilà. Victorina pousse le tabouret, après le souffle. Tu as laissé son souffle passer. La bouche est libre. La rampe n'a plus pris les cheveux. Personne n'a soufflé à sa place. Ça a failli ne pas tenir. Le tabouret avance, après son air. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15710,6 +15764,7 @@
 enfant-f|La bouche est libre.
 maman|La rampe n'a plus pris les cheveux.
 narrateur|Personne n'a soufflé à sa place.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret avance, après son air.</t>
         </is>
       </c>
@@ -15742,17 +15797,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli garder le cheveu. J'ai soufflé, moi. Puis on a monté, après l'air. On descend, la rampe est libre. Le tabouret reste bas, près du mur. Son souffle a passé, d'abord. Le grain de cire claire tremble au pied, sous l'air arrêté.</t>
+          <t>Le tabouret a failli garder le cheveu. J'ai soufflé, moi. Puis on a monté, après l'air. On descend, la rampe est libre. Le tabouret reste bas, près du mur. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le grain de cire claire tremble au pied, sous l'air arrêté.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli garder le cheveu. J'ai soufflé, moi. Puis on a monté, après l'air. On descend, la rampe est libre. Le tabouret reste bas, près du mur. Son souffle a passé, d'abord. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; tremble au pied, sous l'air arrêté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli garder le cheveu. J'ai soufflé, moi. Puis on a monté, après l'air. On descend, la rampe est libre. Le tabouret reste bas, près du mur. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; tremble au pied, sous l'air arrêté.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli garder le cheveu. J'ai soufflé, moi. Puis on a monté, après l'air. On descend, la rampe est libre. Le tabouret reste bas, près du mur. Son souffle a passé, d'abord. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; tremble au pied, sous l'air arrêté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli garder le cheveu. J'ai soufflé, moi. Puis on a monté, après l'air. On descend, la rampe est libre. Le tabouret reste bas, près du mur. Son souffle a passé, d'abord. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; tremble au pied, sous l'air arrêté.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -15896,6 +15951,7 @@
 papa|On descend, la rampe est libre.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|Son souffle a passé, d'abord.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire tremble au pied, sous l'air arrêté.</t>
         </is>
       </c>
@@ -16121,17 +16177,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?</t>
+          <t>La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/slow&gt; [long-pause]</t>
+          <t>&lt;slow&gt;La manche cache le clou, trop longue. Victorina refuse de foncer, cette fois. Elle observe le cadre, et elle écoute le palier. Tu vois le grain, toi ? La manche, le bouton, ou le clou ?&lt;/slow&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -16291,6 +16347,7 @@
         <is>
           <t>narrateur|La manche cache le clou, trop longue.
 narrateur|Victorina refuse de foncer, cette fois.
+narrateur|Elle observe le cadre, et elle écoute le palier.
 maman|Tu vois le grain, toi ?
 papa|La manche, le bouton, ou le clou ?</t>
         </is>
@@ -16319,17 +16376,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Ta manche, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, près du tabouret. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le tabouret, sans presser. Tu as laissé sa manche finir. On monte, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le tabouret avance, la manche haute.</t>
+          <t>Ta manche, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, près du tabouret. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le tabouret, sans presser. Tu as laissé sa manche finir. On monte, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le tabouret avance, la manche haute.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ta &lt;emphasis level="moderate"&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, près du tabouret. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le tabouret, sans presser. Tu as laissé sa manche finir. On monte, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le tabouret avance, la manche haute.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ta &lt;emphasis level="moderate"&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, près du tabouret. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le tabouret, sans presser. Tu as laissé sa manche finir. On monte, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le tabouret avance, la manche haute.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Ta &lt;emphasis&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, près du tabouret. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le tabouret, sans presser. Tu as laissé sa manche finir. On monte, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Le tabouret avance, la manche haute. [pause]</t>
+          <t>Ta &lt;emphasis&gt;manche&lt;/emphasis&gt;, on la relève. Elle tire trop vite, puis s'arrête. Mila relève la manche, près du tabouret. Le grain de cire claire sort du tissu. Je vois le clou. Victorina tient le tabouret, sans presser. Tu as laissé sa manche finir. On monte, maintenant. Le manteau attend, un peu. Personne n'a tiré le bras. Ça a failli ne pas tenir. Le tabouret avance, la manche haute. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16473,6 +16530,7 @@
 enfant-f|On monte, maintenant.
 maman|Le manteau attend, un peu.
 narrateur|Personne n'a tiré le bras.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret avance, la manche haute.</t>
         </is>
       </c>
@@ -16505,17 +16563,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le tabouret reste bas, près du mur. Sa manche a fini, à son rythme. Le grain de cire claire sort du pied, au clou.</t>
+          <t>Le tabouret a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le tabouret reste bas, près du mur. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le grain de cire claire sort du pied, au clou.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le tabouret reste bas, près du mur. Sa manche a fini, à son rythme. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sort du pied, au clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le tabouret reste bas, près du mur. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; sort du pied, au clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le tabouret reste bas, près du mur. Sa manche a fini, à son rythme. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sort du pied, au clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli rester sous la manche. J'ai relevé, moi. Puis on a vu le clou. On descend, le manteau sous le bras. Le tabouret reste bas, près du mur. Sa manche a fini, à son rythme. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; sort du pied, au clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16659,6 +16717,7 @@
 papa|On descend, le manteau sous le bras.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|Sa manche a fini, à son rythme.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire sort du pied, au clou.</t>
         </is>
       </c>
@@ -16691,17 +16750,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Le bouton, d'abord. Elle tend le poignet, près du tabouret. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le tabouret avance, le poignet net.</t>
+          <t>Le bouton, d'abord. Elle tend le poignet, près du tabouret. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le tabouret avance, le poignet net.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, près du tabouret. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le tabouret avance, le poignet net.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, près du tabouret. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le tabouret avance, le poignet net.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, près du tabouret. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Le tabouret avance, le poignet net. [pause]</t>
+          <t>Le &lt;emphasis&gt;bouton&lt;/emphasis&gt;, d'abord. Elle tend le poignet, près du tabouret. Mila boutonne la manche, lentement. Le grain de cire claire reparaît, au clou. C'est fermé. Victorina attend la dernière boucle. Tu as laissé ses doigts boutonner. Le clou est libre. Le manteau peut attendre un bouton. Personne n'a fermé à sa place. Ça a failli ne pas tenir. Le tabouret avance, le poignet net. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -16845,6 +16904,7 @@
 enfant-f|Le clou est libre.
 maman|Le manteau peut attendre un bouton.
 narrateur|Personne n'a fermé à sa place.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret avance, le poignet net.</t>
         </is>
       </c>
@@ -16877,17 +16937,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli attendre le bouton. C'est fermé, maintenant. Puis on a monté, le poignet net. On descend, un bouton brille. Le tabouret reste bas, près du mur. Ses doigts ont boutonné, lentement. Le grain de cire claire brille au pied, près du bouton.</t>
+          <t>Le tabouret a failli attendre le bouton. C'est fermé, maintenant. Puis on a monté, le poignet net. On descend, un bouton brille. Le tabouret reste bas, près du mur. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le grain de cire claire brille au pied, près du bouton.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli attendre le bouton. C'est fermé, maintenant. Puis on a monté, le poignet net. On descend, un bouton brille. Le tabouret reste bas, près du mur. Ses doigts ont boutonné, lentement. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille au pied, près du bouton.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli attendre le bouton. C'est fermé, maintenant. Puis on a monté, le poignet net. On descend, un bouton brille. Le tabouret reste bas, près du mur. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; brille au pied, près du bouton.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli attendre le bouton. C'est fermé, maintenant. Puis on a monté, le poignet net. On descend, un bouton brille. Le tabouret reste bas, près du mur. Ses doigts ont boutonné, lentement. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille au pied, près du bouton.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli attendre le bouton. C'est fermé, maintenant. Puis on a monté, le poignet net. On descend, un bouton brille. Le tabouret reste bas, près du mur. Ses doigts ont boutonné, lentement. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; brille au pied, près du bouton.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -17031,6 +17091,7 @@
 papa|On descend, un bouton brille.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|Ses doigts ont boutonné, lentement.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire brille au pied, près du bouton.</t>
         </is>
       </c>
@@ -17063,17 +17124,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le clou, on le cherche. Elle pose le tabouret, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina monte vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le tabouret porte, sur le grain.</t>
+          <t>Le clou, on le cherche. Elle pose le tabouret, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina monte vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le tabouret porte, sur le grain.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;clou&lt;/emphasis&gt;, on le cherche. Elle pose le tabouret, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina monte vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le tabouret porte, sur le grain.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;clou&lt;/emphasis&gt;, on le cherche. Elle pose le tabouret, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina monte vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le tabouret porte, sur le grain.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;clou&lt;/emphasis&gt;, on le cherche. Elle pose le tabouret, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina monte vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Le tabouret porte, sur le grain. [pause]</t>
+          <t>Le &lt;emphasis&gt;clou&lt;/emphasis&gt;, on le cherche. Elle pose le tabouret, sans lever trop haut. Mila montre le grain de cire claire. Là. Le clou apparaît, sous le grain. Victorina monte vers le doigt. Tu as suivi son doigt. On accroche, sur le grain. Le manteau a attendu le clou. Personne n'a nommé le chemin. Ça a failli ne pas tenir. Le tabouret porte, sur le grain. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17217,6 +17278,7 @@
 enfant-f|On accroche, sur le grain.
 maman|Le manteau a attendu le clou.
 narrateur|Personne n'a nommé le chemin.
+narrateur|Ça a failli ne pas tenir.
 narrateur|Le tabouret porte, sur le grain.</t>
         </is>
       </c>
@@ -17249,17 +17311,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le tabouret reste bas, près du mur. Son doigt a trouvé le clou. Le grain de cire claire luit au pied, sur le clou.</t>
+          <t>Le tabouret a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le tabouret reste bas, près du mur. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le grain de cire claire luit au pied, sur le clou.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le tabouret reste bas, près du mur. Son doigt a trouvé le clou. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; luit au pied, sur le clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le tabouret a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le tabouret reste bas, près du mur. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le &lt;emphasis level="moderate"&gt;grain de cire claire&lt;/emphasis&gt; luit au pied, sur le clou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le tabouret reste bas, près du mur. Son doigt a trouvé le clou. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; luit au pied, sur le clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le tabouret a failli manquer le clou. Là, j'ai montré. On a suivi le doigt, jusqu'au grain. On descend, la porte des chambres se tait. Le tabouret reste bas, près du mur. Son doigt a trouvé le clou. Le petit toc du début s'est tu. Le &lt;emphasis&gt;grain de cire claire&lt;/emphasis&gt; luit au pied, sur le clou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -17403,6 +17465,7 @@
 papa|On descend, la porte des chambres se tait.
 maman|Le tabouret reste bas, près du mur.
 enfant-f|Son doigt a trouvé le clou.
+narrateur|Le petit toc du début s'est tu.
 narrateur|Le grain de cire claire luit au pied, sur le clou.</t>
         </is>
       </c>
@@ -17429,7 +17492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17542,6 +17605,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
